--- a/quality_surveys/028_submission_quality_peer_reviewer_feedback_form--quality_surveys.xlsx
+++ b/quality_surveys/028_submission_quality_peer_reviewer_feedback_form--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>submission_quality_peer_reviewer_form_page_1</t>
+          <t>1. What is your overall impression of the submission?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reviewer_comments</t>
+          <t>2. Please provide your comments on the submission.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>reviewer_suggestions</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>reviewer_suggestions</t>
+          <t>3. Do you agree or disagree with the submission?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>submission_quality_peer_reviewer_feedback_form_page_3</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reviewer_suggestions</t>
+          <t>4. What specific suggestions do you have for the submission?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>reviewer_suggestions</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reviewer_suggestions</t>
+          <t>5. What is the quality score you give this submission?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>reviewer_suggestions</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>reviewer_suggestions</t>
+          <t>6. Do you have any additional comments for the submission?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>reviewer_comments</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>reviewer_comments</t>
+          <t>7. Do you agree or disagree with the submission?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,16 +681,108 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reviewer_comments</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reviewer_comments</t>
+          <t>8. What specific improvements do you suggest for the submission?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9. What is your rating for the submission quality?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10. Can you suggest any references or resources for the submission?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11. Do you have any other comments or suggestions?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12. Any other comments or suggestions?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -757,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -774,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neither agree nor disagree'}</t>
+          <t>Neither Agree nor Disagree</t>
         </is>
       </c>
     </row>
@@ -791,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -808,97 +900,233 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reviewer_suggestions_choices</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_5_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly agree'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reviewer_suggestions_choices</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat agree'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reviewer_suggestions_choices</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neither agree nor disagree'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>reviewer_suggestions_choices</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'disagree'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>reviewer_suggestions_choices</t>
+          <t>submission_quality_peer_reviewer_feedback_form_page_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly disagree'}</t>
+          <t>Strongly Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_7_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>somewhat_agree</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Somewhat Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_7_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>neither_agree_nor_disagree</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Neither Agree nor Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_7_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_7_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>strongly_disagree</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Strongly Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>submission_quality_peer_reviewer_feedback_form_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
